--- a/4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.36.xlsx
+++ b/4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.36.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="oocihm.22250.36" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="oocihm.22250.36" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -464,12 +464,12 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - paddle</t>
+          <t>Possible duplicate lines - paddle</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - abbyy</t>
+          <t>Possible duplicate lines - abbyy</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -581,12 +581,12 @@
       </c>
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.36.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.36.txt</t>
         </is>
       </c>
       <c r="C2" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0036.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0036.txt</t>
         </is>
       </c>
       <c r="D2" s="1" t="inlineStr"/>
@@ -811,7 +811,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap issue count</t>
+          <t>Possible duplicate lines issue count</t>
         </is>
       </c>
       <c r="B7" s="1" t="inlineStr">

--- a/4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.36.xlsx
+++ b/4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.36.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="oocihm.22250.36" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="oocihm.22250.36" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -422,16 +422,16 @@
     <col width="39" customWidth="1" min="1" max="1"/>
     <col width="60" customWidth="1" min="2" max="2"/>
     <col width="60" customWidth="1" min="3" max="3"/>
-    <col width="33" customWidth="1" min="4" max="4"/>
-    <col width="32" customWidth="1" min="5" max="5"/>
+    <col width="35" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
     <col width="36" customWidth="1" min="6" max="6"/>
     <col width="35" customWidth="1" min="7" max="7"/>
     <col width="27" customWidth="1" min="8" max="8"/>
     <col width="26" customWidth="1" min="9" max="9"/>
-    <col width="60" customWidth="1" min="10" max="10"/>
+    <col width="27" customWidth="1" min="10" max="10"/>
     <col width="60" customWidth="1" min="11" max="11"/>
     <col width="32" customWidth="1" min="12" max="12"/>
-    <col width="31" customWidth="1" min="13" max="13"/>
+    <col width="60" customWidth="1" min="13" max="13"/>
     <col width="36" customWidth="1" min="14" max="14"/>
     <col width="60" customWidth="1" min="15" max="15"/>
     <col width="31" customWidth="1" min="16" max="16"/>
@@ -595,22 +595,22 @@
       <c r="G2" s="1" t="inlineStr"/>
       <c r="H2" s="1" t="inlineStr"/>
       <c r="I2" s="1" t="inlineStr"/>
-      <c r="J2" s="1" t="inlineStr">
-        <is>
-          <t>L4: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+FFFD REPLACEMENT CHARACTER :: â€œamended the word " bill.â€� For such New</t>
-        </is>
-      </c>
+      <c r="J2" s="1" t="inlineStr"/>
       <c r="K2" s="1" t="inlineStr">
         <is>
-          <t>L26: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | symbol-only separator/garbage line :: [BOM]29</t>
         </is>
       </c>
       <c r="L2" s="1" t="inlineStr"/>
-      <c r="M2" s="1" t="inlineStr"/>
+      <c r="M2" s="1" t="inlineStr">
+        <is>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | symbol-only separator/garbage line :: [BOM]29</t>
+        </is>
+      </c>
       <c r="N2" s="1" t="inlineStr"/>
       <c r="O2" s="1" t="inlineStr">
         <is>
-          <t>L18: isolated marker/symbol line :: 1</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | symbol-only separator/garbage line :: [BOM]29</t>
         </is>
       </c>
       <c r="P2" s="1" t="inlineStr"/>
@@ -637,7 +637,7 @@
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>52</t>
         </is>
       </c>
       <c r="D3" s="1" t="inlineStr"/>
@@ -649,7 +649,7 @@
       <c r="J3" s="1" t="inlineStr"/>
       <c r="K3" s="1" t="inlineStr">
         <is>
-          <t>L44: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: s :â€” %</t>
+          <t>L26: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="L3" s="1" t="inlineStr"/>
@@ -657,7 +657,7 @@
       <c r="N3" s="1" t="inlineStr"/>
       <c r="O3" s="1" t="inlineStr">
         <is>
-          <t>L26: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L18: isolated marker/symbol line :: 1</t>
         </is>
       </c>
       <c r="P3" s="1" t="inlineStr"/>
@@ -696,7 +696,7 @@
       <c r="J4" s="1" t="inlineStr"/>
       <c r="K4" s="1" t="inlineStr">
         <is>
-          <t>L59: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L59: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="L4" s="1" t="inlineStr"/>
@@ -704,7 +704,7 @@
       <c r="N4" s="1" t="inlineStr"/>
       <c r="O4" s="1" t="inlineStr">
         <is>
-          <t>L35: isolated marker/symbol line :: 1</t>
+          <t>L26: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="P4" s="1" t="inlineStr"/>
@@ -726,7 +726,7 @@
       </c>
       <c r="B5" s="1" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C5" s="1" t="inlineStr">
@@ -743,7 +743,7 @@
       <c r="J5" s="1" t="inlineStr"/>
       <c r="K5" s="1" t="inlineStr">
         <is>
-          <t>L63: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L63: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="L5" s="1" t="inlineStr"/>
@@ -751,7 +751,7 @@
       <c r="N5" s="1" t="inlineStr"/>
       <c r="O5" s="1" t="inlineStr">
         <is>
-          <t>L38: isolated marker/symbol line :: *</t>
+          <t>L35: isolated marker/symbol line :: 1</t>
         </is>
       </c>
       <c r="P5" s="1" t="inlineStr"/>
@@ -794,7 +794,7 @@
       <c r="N6" s="1" t="inlineStr"/>
       <c r="O6" s="1" t="inlineStr">
         <is>
-          <t>L54: isolated marker/symbol line :: r.)</t>
+          <t>L38: isolated marker/symbol line :: *</t>
         </is>
       </c>
       <c r="P6" s="1" t="inlineStr"/>
@@ -837,7 +837,7 @@
       <c r="N7" s="1" t="inlineStr"/>
       <c r="O7" s="1" t="inlineStr">
         <is>
-          <t>L57: symbol-only separator/garbage line :: 1030</t>
+          <t>L54: isolated marker/symbol line :: r.)</t>
         </is>
       </c>
       <c r="P7" s="1" t="inlineStr"/>
@@ -880,7 +880,7 @@
       <c r="N8" s="1" t="inlineStr"/>
       <c r="O8" s="1" t="inlineStr">
         <is>
-          <t>L59: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L57: symbol-only separator/garbage line :: 1030</t>
         </is>
       </c>
       <c r="P8" s="1" t="inlineStr"/>
@@ -923,7 +923,7 @@
       <c r="N9" s="1" t="inlineStr"/>
       <c r="O9" s="1" t="inlineStr">
         <is>
-          <t>L61: isolated marker/symbol line :: \</t>
+          <t>L59: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="P9" s="1" t="inlineStr"/>
@@ -945,7 +945,7 @@
       </c>
       <c r="B10" s="1" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C10" s="1" t="inlineStr">
@@ -966,7 +966,7 @@
       <c r="N10" s="1" t="inlineStr"/>
       <c r="O10" s="1" t="inlineStr">
         <is>
-          <t>L63: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L61: isolated marker/symbol line :: \</t>
         </is>
       </c>
       <c r="P10" s="1" t="inlineStr"/>
@@ -993,7 +993,7 @@
       </c>
       <c r="C11" s="1" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D11" s="1" t="inlineStr"/>
@@ -1009,7 +1009,7 @@
       <c r="N11" s="1" t="inlineStr"/>
       <c r="O11" s="1" t="inlineStr">
         <is>
-          <t>L65: isolated marker/symbol line :: A.</t>
+          <t>L63: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="P11" s="1" t="inlineStr"/>
@@ -1036,7 +1036,7 @@
       </c>
       <c r="C12" s="1" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="D12" s="1" t="inlineStr"/>
@@ -1052,7 +1052,7 @@
       <c r="N12" s="1" t="inlineStr"/>
       <c r="O12" s="1" t="inlineStr">
         <is>
-          <t>L67: isolated marker/symbol line :: t</t>
+          <t>L65: isolated marker/symbol line :: A.</t>
         </is>
       </c>
       <c r="P12" s="1" t="inlineStr"/>
@@ -1093,7 +1093,11 @@
       <c r="L13" s="1" t="inlineStr"/>
       <c r="M13" s="1" t="inlineStr"/>
       <c r="N13" s="1" t="inlineStr"/>
-      <c r="O13" s="1" t="inlineStr"/>
+      <c r="O13" s="1" t="inlineStr">
+        <is>
+          <t>L67: isolated marker/symbol line :: t</t>
+        </is>
+      </c>
       <c r="P13" s="1" t="inlineStr"/>
       <c r="Q13" s="1" t="inlineStr"/>
       <c r="R13" s="1" t="inlineStr"/>
